--- a/wolf/Excel/PropsGenerate_道具生成表.xlsx
+++ b/wolf/Excel/PropsGenerate_道具生成表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9015"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -89,151 +89,151 @@
     <t>道具刷新点1</t>
   </si>
   <si>
-    <t>-7230|-1800|241</t>
+    <t>-79446.109375|81882.3125|-9.289999961853027</t>
   </si>
   <si>
     <t>道具刷新点2</t>
   </si>
   <si>
-    <t>-7230|700|241</t>
+    <t>-80290.59375|84541.21875|-10.329999923706055</t>
   </si>
   <si>
     <t>道具刷新点3</t>
   </si>
   <si>
-    <t>-6730|-2490|241</t>
+    <t>-79490.703125|83387.0625|-10.779999732971191</t>
   </si>
   <si>
     <t>道具刷新点4</t>
   </si>
   <si>
-    <t>-5800|-2570|241</t>
+    <t>-76741.7890625|80767.09375|-9.489999771118164</t>
   </si>
   <si>
     <t>道具刷新点5</t>
   </si>
   <si>
-    <t>-4000|-2600|241</t>
+    <t>-76103.953125|82022.4296875|-9.390000343322754</t>
   </si>
   <si>
     <t>道具刷新点6</t>
   </si>
   <si>
-    <t>-5124|-2342|241</t>
+    <t>-76356.90625|82972.5078125|-10.779999732971191</t>
   </si>
   <si>
     <t>道具刷新点7</t>
   </si>
   <si>
-    <t>-1060|-280|241</t>
+    <t>-78609.140625|84421.09375|-10.779999732971191</t>
   </si>
   <si>
     <t>道具刷新点8</t>
   </si>
   <si>
-    <t>-2374|-2358|241</t>
+    <t>-81470.2109375|82365.9921875|498.550048828125</t>
   </si>
   <si>
     <t>道具刷新点9</t>
   </si>
   <si>
-    <t>-1394|-1783|241</t>
+    <t>-79255.1171875|80622.953125|-9.609999656677246</t>
   </si>
   <si>
     <t>道具刷新点10</t>
   </si>
   <si>
-    <t>-1647|-624|241</t>
+    <t>-79571.5625|80041.2421875|-10.119999885559082</t>
   </si>
   <si>
     <t>道具刷新点11</t>
   </si>
   <si>
-    <t>-1652|966|241</t>
+    <t>-75396.09375|83219.703125|-10.779999732971191</t>
   </si>
   <si>
     <t>道具刷新点12</t>
   </si>
   <si>
-    <t>-2899|1824|241</t>
+    <t>-74638.9609375|82222.4765625|-9.289999961853027</t>
   </si>
   <si>
     <t>道具刷新点13</t>
   </si>
   <si>
-    <t>-2112|-60|241</t>
+    <t>-77157.15625|82015.6171875|-9.5</t>
   </si>
   <si>
     <t>道具刷新点14</t>
   </si>
   <si>
-    <t>-4465|2023|241</t>
+    <t>-79144.15625|85612.4375|-10.779999732971191</t>
   </si>
   <si>
     <t>道具刷新点15</t>
   </si>
   <si>
-    <t>-6678|1872|241</t>
+    <t>-78793.171875|83576.59375|-10.779999732971191</t>
   </si>
   <si>
     <t>道具刷新点16</t>
   </si>
   <si>
-    <t>-3319|-313|241</t>
+    <t>-78605.40625|81807.5078125|-9.289999961853027</t>
   </si>
   <si>
     <t>道具刷新点17</t>
   </si>
   <si>
-    <t>-3555|733|241</t>
+    <t>-84672.796875|84138.2734375|515.9500122070312</t>
   </si>
   <si>
     <t>道具刷新点18</t>
   </si>
   <si>
-    <t>-4732|1014|241</t>
+    <t>-82966.09375|84092.1171875|515.9500122070312</t>
   </si>
   <si>
     <t>道具刷新点19</t>
   </si>
   <si>
-    <t>-5688|1011|241</t>
+    <t>-85546.15625|85221.4296875|498.54998779296875</t>
   </si>
   <si>
     <t>道具刷新点20</t>
   </si>
   <si>
-    <t>-3857|-1605|241</t>
+    <t>-85206.421875|83149.78125|498.54998779296875</t>
   </si>
   <si>
     <t>道具刷新点21</t>
   </si>
   <si>
-    <t>-5039|-1651|241</t>
+    <t>-84378.5234375|82555.3515625|498.54998779296875</t>
   </si>
   <si>
     <t>道具刷新点22</t>
   </si>
   <si>
-    <t>-6341|617|241</t>
+    <t>-82397.34375|82851.140625|498.550048828125</t>
   </si>
   <si>
     <t>道具刷新点23</t>
   </si>
   <si>
-    <t>-6506|-141|241</t>
+    <t>-81604.78125|83680.0078125|498.54998779296875</t>
   </si>
   <si>
     <t>道具刷新点24</t>
   </si>
   <si>
-    <t>-6175|-1585|241</t>
+    <t>-81404.09375|84625.1875|498.550048828125</t>
   </si>
   <si>
     <t>道具刷新点25</t>
   </si>
   <si>
-    <t>-6499|-986|241</t>
+    <t>-82204.7421875|85281.359375|498.54998779296875</t>
   </si>
   <si>
     <t>地图2XXXX</t>
@@ -1346,7 +1346,7 @@
     <col min="4" max="20" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23" customHeight="1" spans="1:5">
+    <row r="1" ht="23" customHeight="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="23" customHeight="1" spans="1:5">
+    <row r="2" ht="23" customHeight="1" spans="1:8">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="23" customHeight="1" spans="1:5">
+    <row r="3" ht="23" customHeight="1" spans="1:8">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="23" customHeight="1" spans="1:3">
+    <row r="9" ht="23" customHeight="1" spans="1:8">
       <c r="A9">
         <v>10001</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" ht="23" customHeight="1" spans="1:3">
+    <row r="10" ht="23" customHeight="1" spans="1:8">
       <c r="A10">
         <v>10002</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" ht="23" customHeight="1" spans="1:3">
+    <row r="11" ht="23" customHeight="1" spans="1:8">
       <c r="A11">
         <v>10003</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" ht="23" customHeight="1" spans="1:3">
+    <row r="12" ht="23" customHeight="1" spans="1:8">
       <c r="A12">
         <v>10004</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="23" customHeight="1" spans="1:3">
+    <row r="13" ht="23" customHeight="1" spans="1:8">
       <c r="A13">
         <v>10005</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" ht="23" customHeight="1" spans="1:3">
+    <row r="14" ht="23" customHeight="1" spans="1:8">
       <c r="A14">
         <v>10006</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" ht="23" customHeight="1" spans="1:3">
+    <row r="15" ht="23" customHeight="1" spans="1:8">
       <c r="A15">
         <v>10007</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" ht="23" customHeight="1" spans="1:3">
+    <row r="16" ht="23" customHeight="1" spans="1:8">
       <c r="A16">
         <v>10008</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" ht="23" customHeight="1" spans="1:3">
+    <row r="33" ht="23" customHeight="1" spans="1:5">
       <c r="A33">
         <v>10025</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" ht="23" customHeight="1" spans="1:3">
+    <row r="35" ht="23" customHeight="1" spans="1:5">
       <c r="A35">
         <v>20001</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="23" customHeight="1" spans="1:4">
+    <row r="36" ht="23" customHeight="1" spans="1:5">
       <c r="A36">
         <v>20002</v>
       </c>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" ht="23" customHeight="1" spans="1:3">
+    <row r="37" ht="23" customHeight="1" spans="1:5">
       <c r="A37">
         <v>20003</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" ht="23" customHeight="1" spans="1:3">
+    <row r="38" ht="23" customHeight="1" spans="1:5">
       <c r="A38">
         <v>20004</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" ht="23" customHeight="1" spans="1:4">
+    <row r="39" ht="23" customHeight="1" spans="1:5">
       <c r="A39">
         <v>20005</v>
       </c>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" ht="23" customHeight="1" spans="1:3">
+    <row r="40" ht="23" customHeight="1" spans="1:5">
       <c r="A40">
         <v>20006</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" ht="23" customHeight="1" spans="1:3">
+    <row r="41" ht="23" customHeight="1" spans="1:5">
       <c r="A41">
         <v>20007</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="42" ht="23" customHeight="1" spans="1:3">
+    <row r="42" ht="23" customHeight="1" spans="1:5">
       <c r="A42">
         <v>20008</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" ht="23" customHeight="1" spans="1:3">
+    <row r="43" ht="23" customHeight="1" spans="1:5">
       <c r="A43">
         <v>20009</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44" ht="23" customHeight="1" spans="1:3">
+    <row r="44" ht="23" customHeight="1" spans="1:5">
       <c r="A44">
         <v>20010</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" ht="23" customHeight="1" spans="1:3">
+    <row r="45" ht="23" customHeight="1" spans="1:5">
       <c r="A45">
         <v>20011</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" ht="23" customHeight="1" spans="1:3">
+    <row r="46" ht="23" customHeight="1" spans="1:5">
       <c r="A46">
         <v>20012</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" ht="23" customHeight="1" spans="1:3">
+    <row r="47" ht="23" customHeight="1" spans="1:5">
       <c r="A47">
         <v>20013</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" ht="23" customHeight="1" spans="1:3">
+    <row r="48" ht="23" customHeight="1" spans="1:5">
       <c r="A48">
         <v>20014</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" ht="23" customHeight="1" spans="1:3">
+    <row r="49" ht="23" customHeight="1" spans="1:5">
       <c r="A49">
         <v>20015</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" ht="23" customHeight="1" spans="1:3">
+    <row r="50" ht="23" customHeight="1" spans="1:5">
       <c r="A50">
         <v>20016</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" ht="23" customHeight="1" spans="1:3">
+    <row r="51" ht="23" customHeight="1" spans="1:5">
       <c r="A51">
         <v>20017</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" ht="23" customHeight="1" spans="1:3">
+    <row r="52" ht="23" customHeight="1" spans="1:5">
       <c r="A52">
         <v>20018</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="53" ht="23" customHeight="1" spans="1:3">
+    <row r="53" ht="23" customHeight="1" spans="1:5">
       <c r="A53">
         <v>20019</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="54" ht="23" customHeight="1" spans="1:3">
+    <row r="54" ht="23" customHeight="1" spans="1:5">
       <c r="A54">
         <v>20020</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="55" ht="23" customHeight="1" spans="1:3">
+    <row r="55" ht="23" customHeight="1" spans="1:5">
       <c r="A55">
         <v>20021</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" ht="21" customHeight="1" spans="1:3">
+    <row r="58" ht="21" customHeight="1" spans="1:5">
       <c r="A58" s="3">
         <v>30001</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" ht="21" customHeight="1" spans="1:3">
+    <row r="59" ht="21" customHeight="1" spans="1:5">
       <c r="A59" s="3">
         <v>30002</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="60" ht="21" customHeight="1" spans="1:3">
+    <row r="60" ht="21" customHeight="1" spans="1:5">
       <c r="A60" s="3">
         <v>30003</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" ht="21" customHeight="1" spans="1:3">
+    <row r="61" ht="21" customHeight="1" spans="1:5">
       <c r="A61" s="3">
         <v>30004</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="62" ht="21" customHeight="1" spans="1:3">
+    <row r="62" ht="21" customHeight="1" spans="1:5">
       <c r="A62" s="3">
         <v>30005</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="63" ht="21" customHeight="1" spans="1:3">
+    <row r="63" ht="21" customHeight="1" spans="1:5">
       <c r="A63" s="3">
         <v>30006</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="64" ht="21" customHeight="1" spans="1:3">
+    <row r="64" ht="21" customHeight="1" spans="1:5">
       <c r="A64" s="3">
         <v>30007</v>
       </c>
@@ -2269,10 +2269,10 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:3">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:3">
       <c r="A80" s="3"/>
     </row>
     <row r="81" spans="1:1">
